--- a/docs/中文.xlsx
+++ b/docs/中文.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="585" windowWidth="12615" windowHeight="6750" activeTab="1"/>
+    <workbookView xWindow="720" yWindow="585" windowWidth="12615" windowHeight="6750"/>
   </bookViews>
   <sheets>
     <sheet name="表現態度" sheetId="14" r:id="rId1"/>
     <sheet name="成語故事" sheetId="15" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="16" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="110">
   <si>
     <t>如履薄冰</t>
   </si>
@@ -662,9 +663,6 @@
     </r>
   </si>
   <si>
-    <t>傲慢無禮。</t>
-  </si>
-  <si>
     <t>趾高氣昂</t>
   </si>
   <si>
@@ -1025,10 +1023,6 @@
   </si>
   <si>
     <t>注音</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>說明</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1095,6 +1089,251 @@
 林書聿用力點頭。她知道，謙虛謹慎，才是走得長遠的方法。
 （全劇終）</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>處理這件牽涉廣泛的機密案子時，大家都如履薄冰，深怕出了一點差錯。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造句</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解釋：比喻處事極為謹慎小心。</t>
+  </si>
+  <si>
+    <t>造句：處理這件牽涉廣泛的機密案子時，大家都如履薄冰，深怕出</t>
+  </si>
+  <si>
+    <t>了一點差錯。</t>
+  </si>
+  <si>
+    <t>解釋：重要的或不重要的，都不會遺漏，比喻做事很仔細。</t>
+  </si>
+  <si>
+    <t>絲馬跡。</t>
+  </si>
+  <si>
+    <t>解釋：斤斤計較。</t>
+  </si>
+  <si>
+    <t>造句：他在生意上總是錙銖必較，連一塊錢的利潤也不肯輕易讓</t>
+  </si>
+  <si>
+    <t>步。</t>
+  </si>
+  <si>
+    <r>
+      <t>羽扇綸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>巾</t>
+    </r>
+  </si>
+  <si>
+    <t>解釋：形容態度從容不迫、瀟灑閑適。</t>
+  </si>
+  <si>
+    <t>造句：舞台上飾演諸葛亮的演員羽扇綸巾，神態自若，完美展現了</t>
+  </si>
+  <si>
+    <t>軍師的風采。</t>
+  </si>
+  <si>
+    <t>解釋：議人奴才相十足，卑屈取媚的樣子。</t>
+  </si>
+  <si>
+    <t>造句：他為了升官發財，竟然對長官做出奴顏婢膝的醜態，實在令</t>
+  </si>
+  <si>
+    <t>人不齒。</t>
+  </si>
+  <si>
+    <t>解釋：從鼻子裡發出冷笑。表示不屑、鄙視。</t>
+  </si>
+  <si>
+    <t>造句：對於他那種不切實際又滿是漏洞的提議，在場的專家們都嗤</t>
+  </si>
+  <si>
+    <t>之以鼻。</t>
+  </si>
+  <si>
+    <t>解釋：趨附權貴，以求進升。</t>
+  </si>
+  <si>
+    <t>造句：為了擠進上流社會，他不惜使出各種攀龍附鳳的手段來結交</t>
+  </si>
+  <si>
+    <t>權貴。</t>
+  </si>
+  <si>
+    <t>解釋：依仗本身有才幹而驕傲，目空一切。</t>
+  </si>
+  <si>
+    <t>造句：他雖然聰明絕頂，但恃才傲物的個性讓他得罪了不少同事，</t>
+  </si>
+  <si>
+    <t>導致團隊合作困難。</t>
+  </si>
+  <si>
+    <r>
+      <t>倨傲鮮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>腆</t>
+    </r>
+  </si>
+  <si>
+    <t>解釋：傲慢無禮。</t>
+  </si>
+  <si>
+    <t>造句：這位年輕的暴發戶態度倨傲鮮腆，對待服務人員十分無禮，</t>
+  </si>
+  <si>
+    <t>完全沒有基本的教養。</t>
+  </si>
+  <si>
+    <t>解釋：走路腳抬得很高，十分神氣。</t>
+  </si>
+  <si>
+    <t>造句：贏得比賽後，他趾高氣昂地走上頒獎台，享受著眾人的歡呼</t>
+  </si>
+  <si>
+    <t>與掌聲。</t>
+  </si>
+  <si>
+    <t>解釋：表示傲然輕視或不服氣的意思。</t>
+  </si>
+  <si>
+    <t>造句：他登上大樓頂端，望著腳下渺小的車水馬龍，心中不禁湧起</t>
+  </si>
+  <si>
+    <t>一股睥睨一切的氣勢。</t>
+  </si>
+  <si>
+    <t>解釋：不隨便說笑。通常用來形容人一板一眼，嚴肅而不易親近。</t>
+  </si>
+  <si>
+    <t>造句：我們的數學老師向來不苟言笑，上課氣氛十分嚴肅，讓學生</t>
+  </si>
+  <si>
+    <t>們對他又敬又畏。</t>
+  </si>
+  <si>
+    <t>解釋：比喻容易引起懷疑的場合。</t>
+  </si>
+  <si>
+    <t>造句：為了避免瓜田李下的嫌疑，他在擔任評審期間，嚴格拒絕與</t>
+  </si>
+  <si>
+    <t>任何參賽者私下接觸。</t>
+  </si>
+  <si>
+    <t>解釋：表示氣勢很盛。指盛氣凌人，使入驚懼。</t>
+  </si>
+  <si>
+    <t>造句：在記者會上，面對記者咄咄逼人的提問，發言人依然保持冷</t>
+  </si>
+  <si>
+    <t>靜，有條不紊地回答。</t>
+  </si>
+  <si>
+    <t>造句：警方將案發現場的線索鉅細靡遺地記錄下來，不放過任何蛛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>警方將案發現場的線索鉅細靡遺地記錄下來，不放過任何蛛絲馬跡。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>舞台上飾演諸葛亮的演員羽扇綸巾，神態自若，完美展現了軍師的風采。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>他在生意上總是錙銖必較，連一塊錢的利潤也不肯輕易讓步。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>他為了升官發財，竟然對長官做出奴顏婢膝的醜態，實在令人不齒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>對於他那種不切實際又滿是漏洞的提議，在場的專家們都嗤之以鼻。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>為了擠進上流社會，他不惜使出各種攀龍附鳳的手段來結交權貴。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>他雖然聰明絕頂，但恃才傲物的個性讓他得罪了不少同事，導致團隊合作困難。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>傲慢無禮。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>這位年輕的暴發戶態度倨傲鮮腆，對待服務人員十分無禮，完全沒有基本的教養。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贏得比賽後，他趾高氣昂地走上頒獎台，享受著眾人的歡呼與掌聲。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>他登上大樓頂端，望著腳下渺小的車水馬龍，心中不禁湧起一股睥睨一切的氣勢。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我們的數學老師向來不苟言笑，上課氣氛十分嚴肅，讓學生們對他又敬又畏。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>為了避免瓜田李下的嫌疑，他在擔任評審期間，嚴格拒絕與任何參賽者私下接觸。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在記者會上，面對記者咄咄逼人的提問，發言人依然保持冷靜，有條不紊地回答。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解釋</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1358,26 +1597,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
     <col min="2" max="2" width="26.140625" customWidth="1"/>
     <col min="3" max="3" width="54.85546875" customWidth="1"/>
+    <col min="4" max="4" width="81.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>109</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1387,8 +1630,11 @@
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1398,8 +1644,11 @@
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1409,8 +1658,11 @@
       <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1420,8 +1672,11 @@
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -1431,8 +1686,11 @@
       <c r="C6" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -1442,8 +1700,11 @@
       <c r="C7" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -1453,8 +1714,11 @@
       <c r="C8" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -1464,8 +1728,11 @@
       <c r="C9" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
@@ -1473,67 +1740,86 @@
         <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>41</v>
+      <c r="D15" s="1" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1548,26 +1834,320 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="306">
       <c r="A2" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="306">
       <c r="A4" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A56"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="98.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/docs/中文.xlsx
+++ b/docs/中文.xlsx
@@ -7,16 +7,14 @@
     <workbookView xWindow="720" yWindow="585" windowWidth="12615" windowHeight="6750"/>
   </bookViews>
   <sheets>
-    <sheet name="表現態度" sheetId="14" r:id="rId1"/>
-    <sheet name="成語故事" sheetId="15" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="16" r:id="rId3"/>
+    <sheet name="表現態度1" sheetId="14" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t>如履薄冰</t>
   </si>
@@ -1022,33 +1020,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>注音</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>少年劍客闖江湖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故事</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>標題</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>少年劍客林庭宇初出茅廬，聽聞「天劍門」廣招弟子，便背著木劍上山。山路陡峭，崖邊積雪未融，他走得如履薄冰，深怕一失足成千古恨。
-山門前，守門長老盤查極嚴，鉅細靡遺，連他包袱裡有幾個饅頭、劍穗是什麼顏色都要一一記下。林庭宇暗想：「名門大派，果然規矩森嚴。」
-入了大殿，只見帳房師叔正與人為了三文銅錢錙銖必較，算盤打得劈啪作響；一旁的大師兄卻手持羽扇、頭戴綸巾，好一副羽扇綸巾的名士風範，淡淡道：「錢財乃身外之物。」帳房師叔氣得鬍子都翹了起來。
-比武選拔開始。林庭宇見一名弟子對著考官奴顏婢膝，又是捶背又是奉茶，口稱「弟子願為長老提鞋十年」；另一名富家公子則恃才傲物，拎著鑲金寶劍冷笑：「就憑你們，也配與我過招？」見旁人練劍，他更嗤之以鼻：「花拳繡腿，不堪一擊。」
-輪到林庭宇上場。主考的掌門師太不苟言笑，面寒如霜；她身旁的執法長老目光睥睨一切，彷彿天下英雄盡是草芥。二長老更是咄咄逼人，劍未出鞘先喝問：「你師承何人？練劍幾年？敢闖天劍門，不怕死嗎？」
-林庭宇抱拳朗聲道：「晚輩無門無派，不願攀龍附鳳、投靠權貴求前程，只求以劍會友，憑真本事立足江湖！」
-師太眼中閃過一絲讚許。
-正此時，場外一陣喧嘩——那富家公子落選了，竟倨傲鮮腆地當眾辱罵長老，被逐出山門時仍趾高氣昂，鼻孔朝天，結果一腳踩空，滾下了三十六級石階，寶劍摔成了兩截。
-林庭宇技壓群雄，順利入門。師太收劍入鞘，只叮囑一句：「藏經閣重地，旁邊便是本門秘笈庫房，無事莫在附近徘徊。瓜田李下，江湖險惡，人言可畏。」
-林庭宇躬身受教。他明白了——劍法可以練，名聲要靠謹言慎行，一步一步掙來。
-（欲知後事如何，且待下回分解）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1100,183 +1072,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>解釋：比喻處事極為謹慎小心。</t>
-  </si>
-  <si>
-    <t>造句：處理這件牽涉廣泛的機密案子時，大家都如履薄冰，深怕出</t>
-  </si>
-  <si>
-    <t>了一點差錯。</t>
-  </si>
-  <si>
-    <t>解釋：重要的或不重要的，都不會遺漏，比喻做事很仔細。</t>
-  </si>
-  <si>
-    <t>絲馬跡。</t>
-  </si>
-  <si>
-    <t>解釋：斤斤計較。</t>
-  </si>
-  <si>
-    <t>造句：他在生意上總是錙銖必較，連一塊錢的利潤也不肯輕易讓</t>
-  </si>
-  <si>
-    <t>步。</t>
-  </si>
-  <si>
-    <r>
-      <t>羽扇綸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>巾</t>
-    </r>
-  </si>
-  <si>
-    <t>解釋：形容態度從容不迫、瀟灑閑適。</t>
-  </si>
-  <si>
-    <t>造句：舞台上飾演諸葛亮的演員羽扇綸巾，神態自若，完美展現了</t>
-  </si>
-  <si>
-    <t>軍師的風采。</t>
-  </si>
-  <si>
-    <t>解釋：議人奴才相十足，卑屈取媚的樣子。</t>
-  </si>
-  <si>
-    <t>造句：他為了升官發財，竟然對長官做出奴顏婢膝的醜態，實在令</t>
-  </si>
-  <si>
-    <t>人不齒。</t>
-  </si>
-  <si>
-    <t>解釋：從鼻子裡發出冷笑。表示不屑、鄙視。</t>
-  </si>
-  <si>
-    <t>造句：對於他那種不切實際又滿是漏洞的提議，在場的專家們都嗤</t>
-  </si>
-  <si>
-    <t>之以鼻。</t>
-  </si>
-  <si>
-    <t>解釋：趨附權貴，以求進升。</t>
-  </si>
-  <si>
-    <t>造句：為了擠進上流社會，他不惜使出各種攀龍附鳳的手段來結交</t>
-  </si>
-  <si>
-    <t>權貴。</t>
-  </si>
-  <si>
-    <t>解釋：依仗本身有才幹而驕傲，目空一切。</t>
-  </si>
-  <si>
-    <t>造句：他雖然聰明絕頂，但恃才傲物的個性讓他得罪了不少同事，</t>
-  </si>
-  <si>
-    <t>導致團隊合作困難。</t>
-  </si>
-  <si>
-    <r>
-      <t>倨傲鮮</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>腆</t>
-    </r>
-  </si>
-  <si>
-    <t>解釋：傲慢無禮。</t>
-  </si>
-  <si>
-    <t>造句：這位年輕的暴發戶態度倨傲鮮腆，對待服務人員十分無禮，</t>
-  </si>
-  <si>
-    <t>完全沒有基本的教養。</t>
-  </si>
-  <si>
-    <t>解釋：走路腳抬得很高，十分神氣。</t>
-  </si>
-  <si>
-    <t>造句：贏得比賽後，他趾高氣昂地走上頒獎台，享受著眾人的歡呼</t>
-  </si>
-  <si>
-    <t>與掌聲。</t>
-  </si>
-  <si>
-    <t>解釋：表示傲然輕視或不服氣的意思。</t>
-  </si>
-  <si>
-    <t>造句：他登上大樓頂端，望著腳下渺小的車水馬龍，心中不禁湧起</t>
-  </si>
-  <si>
-    <t>一股睥睨一切的氣勢。</t>
-  </si>
-  <si>
-    <t>解釋：不隨便說笑。通常用來形容人一板一眼，嚴肅而不易親近。</t>
-  </si>
-  <si>
-    <t>造句：我們的數學老師向來不苟言笑，上課氣氛十分嚴肅，讓學生</t>
-  </si>
-  <si>
-    <t>們對他又敬又畏。</t>
-  </si>
-  <si>
-    <t>解釋：比喻容易引起懷疑的場合。</t>
-  </si>
-  <si>
-    <t>造句：為了避免瓜田李下的嫌疑，他在擔任評審期間，嚴格拒絕與</t>
-  </si>
-  <si>
-    <t>任何參賽者私下接觸。</t>
-  </si>
-  <si>
-    <t>解釋：表示氣勢很盛。指盛氣凌人，使入驚懼。</t>
-  </si>
-  <si>
-    <t>造句：在記者會上，面對記者咄咄逼人的提問，發言人依然保持冷</t>
-  </si>
-  <si>
-    <t>靜，有條不紊地回答。</t>
-  </si>
-  <si>
-    <t>造句：警方將案發現場的線索鉅細靡遺地記錄下來，不放過任何蛛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>警方將案發現場的線索鉅細靡遺地記錄下來，不放過任何蛛絲馬跡。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1334,6 +1129,112 @@
   </si>
   <si>
     <t>解釋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>少年劍客林庭宇初出茅廬，聽聞「天劍門」廣招弟子，便背著木劍上山。山路陡峭，崖邊積雪未融，他走得如履薄冰，深怕一失足成千古恨。
+山門前，守門長老盤查極嚴，鉅細靡遺，連他包袱裡有幾個饅頭、劍穗是什麼顏色都要一一記下。林庭宇暗想：「名門大派，果然規矩森嚴。」
+入了大殿，只見帳房師叔正與人為了三文銅錢錙銖必較，算盤打得劈啪作響；一旁的大師兄卻手持羽扇、頭戴綸巾，好一副羽扇綸巾的名士風範，淡淡道：「錢財乃身外之物。」帳房師叔氣得鬍子都翹了起來。
+比武選拔開始。林庭宇見一名弟子對著考官奴顏婢膝，又是捶背又是奉茶，口稱「弟子願為長老提鞋十年」；另一名富家公子則恃才傲物，拎著鑲金寶劍冷笑：「就憑你們，也配與我過招？」見旁人練劍，他更嗤之以鼻：「花拳繡腿，不堪一擊。」
+輪到林庭宇上場。主考的掌門師太不苟言笑，面寒如霜；她身旁的執法長老目光睥睨一切，彷彿天下英雄盡是草芥。二長老更是咄咄逼人，劍未出鞘先喝問：「你師承何人？練劍幾年？敢闖天劍門，不怕死嗎？」
+林庭宇抱拳朗聲道：「晚輩無門無派，不願攀龍附鳳、投靠權貴求前程，只求以劍會友，憑真本事立足江湖！」
+師太眼中閃過一絲讚許。
+正此時，場外一陣喧嘩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>——</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>那富家公子落選了，竟倨傲鮮腆地當眾辱罵長老，被逐出山門時仍趾高氣昂，鼻孔朝天，結果一腳踩空，滾下了三十六級石階，寶劍摔成了兩截。
+林庭宇技壓群雄，順利入門。師太收劍入鞘，只叮囑一句：「藏經閣重地，旁邊便是本門秘笈庫房，無事莫在附近徘徊。瓜田李下，江湖險惡，人言可畏。」
+林庭宇躬身受教。他明白了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>——</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>劍法可以練，名聲要靠謹言慎行，一步一步掙來。
+（欲知後事如何，且待下回分解）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>#</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>成語</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故事</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>#</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>故事</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注音</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>標題</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1341,7 +1242,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1361,6 +1262,13 @@
       <name val="Arial"/>
       <family val="3"/>
       <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1384,12 +1292,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1597,223 +1506,254 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" customWidth="1"/>
-    <col min="4" max="4" width="81.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" customWidth="1"/>
+    <col min="3" max="3" width="73.5703125" customWidth="1"/>
+    <col min="4" max="4" width="54.85546875" customWidth="1"/>
+    <col min="5" max="5" width="81.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="B6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="B11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="B12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="B13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="306">
+      <c r="B18" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>50</v>
+      <c r="C18" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>108</v>
+    <row r="19" spans="1:3" ht="306">
+      <c r="B19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1821,337 +1761,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
-  <cols>
-    <col min="1" max="1" width="20.140625" customWidth="1"/>
-    <col min="2" max="2" width="73.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="306">
-      <c r="A2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="306">
-      <c r="A4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A56"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
-  <cols>
-    <col min="1" max="1" width="98.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/docs/中文.xlsx
+++ b/docs/中文.xlsx
@@ -4,17 +4,18 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="585" windowWidth="12615" windowHeight="6750"/>
+    <workbookView xWindow="720" yWindow="585" windowWidth="12615" windowHeight="6750" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="表現態度1" sheetId="14" r:id="rId1"/>
+    <sheet name="表現態度2" sheetId="17" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="123">
   <si>
     <t>如履薄冰</t>
   </si>
@@ -1069,6 +1070,9 @@
   </si>
   <si>
     <t>造句</t>
+  </si>
+  <si>
+    <t>造句</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1192,6 +1196,9 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>成語</t>
+  </si>
+  <si>
     <r>
       <t>#</t>
     </r>
@@ -1231,11 +1238,1065 @@
   </si>
   <si>
     <t>注音</t>
+  </si>
+  <si>
+    <t>注音</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>標題</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拂袖而去</t>
+  </si>
+  <si>
+    <r>
+      <t>ㄈㄨˊ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄒㄧㄡˋ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄦˊ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄑㄩˋ</t>
+    </r>
+  </si>
+  <si>
+    <t>形容言語不合，心裡不滿的離去。</t>
+  </si>
+  <si>
+    <t>兩人談判破裂，他氣得拂袖而去。</t>
+  </si>
+  <si>
+    <t>無病呻吟</t>
+  </si>
+  <si>
+    <r>
+      <t>ㄨˊ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄅㄧㄥˋ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄕㄣ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄧㄣˊ</t>
+    </r>
+  </si>
+  <si>
+    <t>比喻人無端憂戚或妄發牢騷。</t>
+  </si>
+  <si>
+    <t>明明生活順遂，卻整天無病呻吟，讓人厭煩。</t>
+  </si>
+  <si>
+    <t>妄自菲薄</t>
+  </si>
+  <si>
+    <r>
+      <t>ㄨㄤˋ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄗˋ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄈㄟ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">ˇ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄅㄛˊ</t>
+    </r>
+  </si>
+  <si>
+    <t>過於自卑而不知自重。</t>
+  </si>
+  <si>
+    <t>你的能力很好，不必妄自菲薄。</t>
+  </si>
+  <si>
+    <t>自怨自艾</t>
+  </si>
+  <si>
+    <r>
+      <t>ㄗˋ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄩㄢˋ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄗˋ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄧˋ</t>
+    </r>
+  </si>
+  <si>
+    <t>悔恨自己過去的錯誤而加以改正缺失。</t>
+  </si>
+  <si>
+    <t>與其自怨自艾，不如振作起來重新出發。</t>
+  </si>
+  <si>
+    <t>待價而沽</t>
+  </si>
+  <si>
+    <r>
+      <t>ㄉㄞˋ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄐㄧㄚˋ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄦˊ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄍㄨ</t>
+    </r>
+  </si>
+  <si>
+    <t>比喻人等待機會，為世所用。</t>
+  </si>
+  <si>
+    <t>他手握一身好本事，正待價而沽等待伯樂賞識。</t>
+  </si>
+  <si>
+    <t>寧為雞首，不為牛後</t>
+  </si>
+  <si>
+    <r>
+      <t>ㄋㄧㄥˋ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄨㄟˊ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄐㄧ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄕㄡ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ˇ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，ㄅㄨˊ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄨㄟˊ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄋㄧㄡˊ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄏㄡˋ</t>
+    </r>
+  </si>
+  <si>
+    <t>比喻寧願在小場面中作主，不願在大場面聽人支配。</t>
+  </si>
+  <si>
+    <t>他選擇自己創業，正是寧為雞首，不為牛後的想法。</t>
+  </si>
+  <si>
+    <t>騎牆之見</t>
+  </si>
+  <si>
+    <r>
+      <t>ㄑㄧˊ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄑㄧㄤˊ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄓ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄐㄧㄢˋ</t>
+    </r>
+  </si>
+  <si>
+    <t>比喻心存觀望，態度立場模稜兩可。</t>
+  </si>
+  <si>
+    <t>面對兩派爭論，他總是抱持騎牆之見，不肯表態。</t>
+  </si>
+  <si>
+    <t>作壁上觀</t>
+  </si>
+  <si>
+    <r>
+      <t>ㄗㄨㄛˋ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄅㄧˋ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄕㄤˋ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄍㄨㄢ</t>
+    </r>
+  </si>
+  <si>
+    <t>坐觀成敗，不幫助任何一方。</t>
+  </si>
+  <si>
+    <t>同學間起了爭執，他只是作壁上觀，不加勸阻。</t>
+  </si>
+  <si>
+    <t>置若罔聞</t>
+  </si>
+  <si>
+    <r>
+      <t>ㄓˋ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄖㄨㄛˋ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄨㄤ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">ˇ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄨㄣˊ</t>
+    </r>
+  </si>
+  <si>
+    <t>雖有耳聞，卻好像沒有聽到一樣不加理會。</t>
+  </si>
+  <si>
+    <t>大家好言相勸，他卻置若罔聞，依然故我。</t>
+  </si>
+  <si>
+    <t>俯首貼耳</t>
+  </si>
+  <si>
+    <r>
+      <t>ㄈㄨ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">ˇ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄕㄡ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">ˇ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄊㄧㄝ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄦ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ˇ</t>
+    </r>
+  </si>
+  <si>
+    <t>低頭垂耳，形容恭順馴服的樣子。</t>
+  </si>
+  <si>
+    <t>他對上司俯首貼耳，唯命是從。</t>
+  </si>
+  <si>
+    <t>劍及履及</t>
+  </si>
+  <si>
+    <r>
+      <t>ㄐㄧㄢˋ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄐㄧˊ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄌㄩ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">ˇ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄐㄧˊ</t>
+    </r>
+  </si>
+  <si>
+    <t>形容人行動果決、快速，迫不及待的樣子。</t>
+  </si>
+  <si>
+    <t>接到任務後他劍及履及，立刻著手處理。</t>
+  </si>
+  <si>
+    <t>剛愎自用</t>
+  </si>
+  <si>
+    <r>
+      <t>ㄍㄤ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄅㄧˋ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄗˋ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄩㄥˋ</t>
+    </r>
+  </si>
+  <si>
+    <t>性情倔強，固執己見。</t>
+  </si>
+  <si>
+    <t>他剛愎自用，從不聽取別人的建議。</t>
+  </si>
+  <si>
+    <t>師心自用</t>
+  </si>
+  <si>
+    <r>
+      <t>ㄕ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄒㄧㄣ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄗˋ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ㄩㄥˋ</t>
+    </r>
+  </si>
+  <si>
+    <t>剛愎任性，自以為是。</t>
+  </si>
+  <si>
+    <t>他做事總是師心自用，不肯採納他人意見。</t>
   </si>
 </sst>
 </file>
@@ -1518,19 +2579,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1558,7 +2619,7 @@
         <v>5</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1572,7 +2633,7 @@
         <v>8</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1586,7 +2647,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1600,7 +2661,7 @@
         <v>14</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1614,7 +2675,7 @@
         <v>17</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1628,7 +2689,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1642,7 +2703,7 @@
         <v>23</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1653,10 +2714,10 @@
         <v>25</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1670,7 +2731,7 @@
         <v>28</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1684,7 +2745,7 @@
         <v>31</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1698,7 +2759,7 @@
         <v>34</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1712,7 +2773,7 @@
         <v>37</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1726,18 +2787,18 @@
         <v>40</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="306">
@@ -1745,7 +2806,7 @@
         <v>42</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="306">
@@ -1761,4 +2822,219 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="48.7109375" customWidth="1"/>
+    <col min="4" max="5" width="48.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="B2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="B3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="B6" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="B11" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="B12" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="B13" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>